--- a/templates/Offline_UK__1__Google_-_Template.xlsx
+++ b/templates/Offline_UK__1__Google_-_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Omri PPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF2C2A5-A0F1-4D55-BFB8-248918F59B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D99FA7-25EE-412D-BD23-8A5508A580BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="conversion-import-template" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="29">
   <si>
     <t>Parameters:TimeZone=America/New_York;</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>offline - casinocasino</t>
+  </si>
+  <si>
+    <t>offline - betmgm (1)</t>
   </si>
 </sst>
 </file>
@@ -472,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.5703125" customWidth="1"/>
@@ -803,6 +806,20 @@
         <v>6</v>
       </c>
     </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46024.998611111114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -810,6 +827,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C40BB463539D3240B71C243B80C06056" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca672511a255fc879d499e7cfd3414b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3d935cd2-bfa1-4639-8afd-89415ae12733" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e1e738df3222ccc84a773b64d405138" ns3:_="">
     <xsd:import namespace="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
@@ -947,7 +970,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -956,13 +979,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7960F92F-7BB9-4753-88BC-3C3090539E7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E0D8AB1-343D-48A5-8ED3-1ACDBEBB89D2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -980,26 +1013,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61F8312-CA35-4899-8C65-EC7A689F2EF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7960F92F-7BB9-4753-88BC-3C3090539E7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3d935cd2-bfa1-4639-8afd-89415ae12733"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>